--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -808,667 +808,667 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9568,0.0075,0.0153,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.0035,0.0000,0.0001,0.9988</t>
+    <t>0.9935,0.0024,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.8490,0.0001,0.0000,0.2009</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1237,0.0032,0.8680,0.0007</t>
-  </si>
-  <si>
-    <t>0.0043,0.0004,0.9948,0.0004</t>
-  </si>
-  <si>
-    <t>0.2260,0.0005,0.9073,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.0001,0.9930,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0001,0.0023,0.0002</t>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9767,0.0050,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.0623,0.0004,0.9579,0.0005</t>
+  </si>
+  <si>
+    <t>0.4218,0.0021,0.6927,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0005,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.9298,0.0005,0.0535,0.0007</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0378,0.9654,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9980,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0658,0.0010,0.9117,0.0016</t>
-  </si>
-  <si>
-    <t>0.1056,0.0001,0.8996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.9955,0.0015</t>
-  </si>
-  <si>
-    <t>0.0185,0.0008,0.9780,0.0005</t>
-  </si>
-  <si>
-    <t>0.0069,0.0000,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0005,0.9963,0.0009</t>
-  </si>
-  <si>
-    <t>0.0061,0.0000,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.6412,0.3972,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.8401,0.0806,0.0459,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.0019,0.9985,0.0026</t>
-  </si>
-  <si>
-    <t>0.0033,0.9926,0.0036,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0620,0.9527,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9973,0.0442,0.0000</t>
-  </si>
-  <si>
-    <t>0.0099,0.9042,0.0433,0.0008</t>
-  </si>
-  <si>
-    <t>0.0021,0.0085,0.9886,0.0022</t>
-  </si>
-  <si>
-    <t>0.0139,0.0016,0.9712,0.0013</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9930,0.0002</t>
-  </si>
-  <si>
-    <t>0.0088,0.0010,0.9941,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9987,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9987,0.0062</t>
-  </si>
-  <si>
-    <t>0.0013,0.7779,0.0001,0.9475</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.9967,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9984,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9997,0.0000</t>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.9955,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9983,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9806,0.0007,0.0041,0.0012</t>
+  </si>
+  <si>
+    <t>0.9556,0.0002,0.0398,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9986,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0179,0.0000,0.9934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0089,0.0000,0.9904,0.0003</t>
+  </si>
+  <si>
+    <t>0.0035,0.0000,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.2411,0.8303,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.2060,0.3684,0.2232,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9994,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9921,0.0029,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9938,0.0005,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.1197,0.9040,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9917,0.2238,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.9837,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.0233,0.0004,0.9617,0.0019</t>
+  </si>
+  <si>
+    <t>0.0034,0.0142,0.9892,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9944,0.0006</t>
+  </si>
+  <si>
+    <t>0.0147,0.0034,0.9878,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.9849,0.0192,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9973,0.0367</t>
+  </si>
+  <si>
+    <t>0.0276,0.0612,0.0001,0.9191</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.0012,0.9973,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0006,0.9934,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0033,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0031,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8587,0.9889,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0081,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9691,0.0003,0.0284,0.0002</t>
+  </si>
+  <si>
+    <t>0.3990,0.0005,0.6450,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0063,0.9993,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9777,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8528,0.9638,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.2082,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9938,0.9799,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0002,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0007,0.9997</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9864,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9928,0.9890,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.9510,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9940,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9873,0.9191,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0039,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9989,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9998,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.0003,0.9999,0.0001</t>
+    <t>0.9825,0.0007,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.0588,0.0001,0.9630,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9956,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.9941,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0554,0.9463,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9832,0.0007,0.0057,0.0008</t>
+  </si>
+  <si>
+    <t>0.9278,0.0002,0.0889,0.0002</t>
+  </si>
+  <si>
+    <t>0.6434,0.0440,0.0441,0.0077</t>
+  </si>
+  <si>
+    <t>0.9595,0.0033,0.0080,0.0036</t>
+  </si>
+  <si>
+    <t>0.0053,0.3422,0.0028,0.9334</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.9614,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8437,0.1834,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9781,0.0209,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0016,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9695,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9994,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5669,0.0005,0.5446,0.0001</t>
-  </si>
-  <si>
-    <t>0.0764,0.0004,0.9547,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0034,0.9993,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.9858,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9745,0.9162,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0791,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9833,0.9939,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0006,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0006,0.9998</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0005,0.9992</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9346,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9981,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9316,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9907,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.3528,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0022,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.9730,0.0003,0.0108,0.0015</t>
-  </si>
-  <si>
-    <t>0.0342,0.0002,0.9707,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9961,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9989,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0315,0.9682,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.7882,0.0028,0.1970,0.0011</t>
-  </si>
-  <si>
-    <t>0.8782,0.0001,0.1658,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0001,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9447,0.0077,0.0226,0.0014</t>
-  </si>
-  <si>
-    <t>0.0013,0.0806,0.0186,0.9723</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9932,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.6932,0.3631,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9736,0.0276,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
+    <t>0.9987,0.0002,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.4877,0.9908,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.3552,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.0008,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9061,0.0032,0.0427,0.0057</t>
+  </si>
+  <si>
+    <t>0.0082,0.0001,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.9635,0.0013,0.0113,0.0025</t>
+  </si>
+  <si>
+    <t>0.0080,0.0000,0.0000,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0002,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9133,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0472,0.9558,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.3207,0.8001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.3088,0.0001,0.0007,0.8256</t>
+  </si>
+  <si>
+    <t>0.0009,0.0014,0.9973,0.0033</t>
+  </si>
+  <si>
+    <t>0.9761,0.0000,0.0050,0.0062</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0123,0.9866,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9923,0.0021,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.8671,0.0251,0.0284,0.0016</t>
+  </si>
+  <si>
+    <t>0.9709,0.0019,0.0175,0.0003</t>
+  </si>
+  <si>
+    <t>0.9720,0.0136,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0003</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0003</t>
+    <t>0.9534,0.0311,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.8693,0.2134,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7806,0.3207,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0470,0.0005,0.9579,0.0019</t>
+  </si>
+  <si>
+    <t>0.9942,0.0061,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9831,0.0037,0.0073,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0041,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9975,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0857,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0261,0.0016,0.9684,0.0006</t>
+  </si>
+  <si>
+    <t>0.0172,0.0019,0.9773,0.0005</t>
+  </si>
+  <si>
+    <t>0.2298,0.0017,0.7758,0.0010</t>
+  </si>
+  <si>
+    <t>0.1249,0.0151,0.7823,0.0005</t>
+  </si>
+  <si>
+    <t>0.3894,0.0238,0.5056,0.0004</t>
+  </si>
+  <si>
+    <t>0.1563,0.0010,0.9042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9637,0.0020,0.0154,0.0010</t>
+  </si>
+  <si>
+    <t>0.0798,0.0094,0.9020,0.0013</t>
+  </si>
+  <si>
+    <t>0.0024,0.9970,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9478,0.0780,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.2262,0.8578,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0236,0.9771,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.5233,0.2177,0.0377,0.0008</t>
+  </si>
+  <si>
+    <t>0.8714,0.0004,0.1234,0.0010</t>
+  </si>
+  <si>
+    <t>0.9833,0.0012,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.9291,0.0097,0.0240,0.0020</t>
+  </si>
+  <si>
+    <t>0.8795,0.0005,0.1087,0.0016</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0261,0.0072,0.9394,0.0038</t>
+  </si>
+  <si>
+    <t>0.0048,0.0001,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0058,0.9943,0.0004</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.2141,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8262,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0040,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9807,0.0009,0.0047,0.0014</t>
-  </si>
-  <si>
-    <t>0.1319,0.0001,0.9351,0.0000</t>
-  </si>
-  <si>
-    <t>0.9265,0.0008,0.0400,0.0040</t>
-  </si>
-  <si>
-    <t>0.0205,0.0000,0.0000,0.9965</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9491,0.8745,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.9929,0.0005,0.0023</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.3558,0.7383,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0000,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.6299,0.0001,0.0007,0.4543</t>
-  </si>
-  <si>
-    <t>0.0026,0.0051,0.9940,0.0025</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0003,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.0664,0.9221,0.0071,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9875,0.0027,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.7717,0.0922,0.0171,0.0016</t>
-  </si>
-  <si>
-    <t>0.1686,0.0307,0.7621,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.4865,0.6663,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0088,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0013,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0034,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9854,0.0076,0.0047,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9908,0.0051,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0009,0.9956,0.0021</t>
-  </si>
-  <si>
-    <t>0.0010,0.0028,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0366,0.0130,0.9298,0.0020</t>
-  </si>
-  <si>
-    <t>0.1326,0.0005,0.9182,0.0002</t>
-  </si>
-  <si>
-    <t>0.9236,0.0030,0.0239,0.0053</t>
-  </si>
-  <si>
-    <t>0.2057,0.0247,0.6860,0.0005</t>
-  </si>
-  <si>
-    <t>0.0582,0.0500,0.7262,0.0006</t>
-  </si>
-  <si>
-    <t>0.7731,0.0138,0.1957,0.0003</t>
-  </si>
-  <si>
-    <t>0.9754,0.0009,0.0088,0.0012</t>
-  </si>
-  <si>
-    <t>0.5926,0.0006,0.4840,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9588,0.0654,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.2197,0.8614,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0151,0.9845,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9512,0.0202,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.8861,0.0001,0.1371,0.0004</t>
-  </si>
-  <si>
-    <t>0.7669,0.0071,0.0201,0.0406</t>
-  </si>
-  <si>
-    <t>0.8716,0.0134,0.0572,0.0052</t>
-  </si>
-  <si>
-    <t>0.8402,0.0020,0.1247,0.0015</t>
-  </si>
-  <si>
-    <t>0.0007,0.0009,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9976,0.0004</t>
-  </si>
-  <si>
-    <t>0.0072,0.0072,0.9811,0.0011</t>
-  </si>
-  <si>
-    <t>0.0061,0.0014,0.9893,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.6070,0.8256,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0017,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0039,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0022,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9993,0.0015</t>
-  </si>
-  <si>
-    <t>0.0027,0.0052,0.9924,0.0015</t>
-  </si>
-  <si>
-    <t>0.9246,0.0007,0.0236,0.0092</t>
-  </si>
-  <si>
-    <t>0.0118,0.0007,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.7525,0.9532,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0014,0.9931,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9965,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0042,0.9965,0.0007</t>
-  </si>
-  <si>
-    <t>0.8411,0.0015,0.1172,0.0021</t>
-  </si>
-  <si>
-    <t>0.9668,0.0001,0.0261,0.0005</t>
-  </si>
-  <si>
-    <t>0.9953,0.0001,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9926,0.0086,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0035,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0019,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0050,0.0182,0.9795,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.0039,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.6843,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0035,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9521,0.1130</t>
-  </si>
-  <si>
-    <t>0.4293,0.0005,0.5022,0.0028</t>
-  </si>
-  <si>
-    <t>0.0066,0.0012,0.9853,0.0015</t>
-  </si>
-  <si>
-    <t>0.9774,0.0003,0.0017,0.0100</t>
-  </si>
-  <si>
-    <t>0.0014,0.0008,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0059,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0001,0.0003</t>
+    <t>0.9984,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9997,0.0007</t>
+  </si>
+  <si>
+    <t>0.0311,0.5831,0.3875,0.0002</t>
+  </si>
+  <si>
+    <t>0.9815,0.0002,0.0057,0.0030</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0197,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0002,0.9935,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0036,0.9860,0.0044</t>
+  </si>
+  <si>
+    <t>0.0015,0.0034,0.9943,0.0004</t>
+  </si>
+  <si>
+    <t>0.5376,0.0065,0.2991,0.0040</t>
+  </si>
+  <si>
+    <t>0.9543,0.0008,0.0351,0.0010</t>
+  </si>
+  <si>
+    <t>0.9917,0.0001,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0024,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0018,0.9956,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0096,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.4465,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0032,0.9922,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0003,0.9685,0.0172</t>
+  </si>
+  <si>
+    <t>0.0044,0.0004,0.9929,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9955,0.0077</t>
+  </si>
+  <si>
+    <t>0.9718,0.0000,0.0010,0.0201</t>
+  </si>
+  <si>
+    <t>0.0048,0.0004,0.0000,0.9986</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9949,0.0001,0.0001,0.0015</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1854,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1868,7 +1868,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1882,7 +1882,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1896,7 +1896,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1910,7 +1910,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1924,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1952,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1966,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1980,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2019,10 +2019,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2036,7 +2036,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2050,7 +2050,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2064,7 +2064,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2078,7 +2078,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2092,7 +2092,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2106,7 +2106,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2120,7 +2120,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2134,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2148,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2159,10 +2159,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2173,10 +2173,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2190,7 +2190,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2204,7 +2204,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2218,7 +2218,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2232,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2246,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2257,10 +2257,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,7 +2274,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2288,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2302,7 +2302,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2316,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2330,7 +2330,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2344,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2358,7 +2358,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2372,7 +2372,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2386,7 +2386,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2400,7 +2400,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2414,7 +2414,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2428,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2442,7 +2442,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2456,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2467,10 +2467,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2484,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2498,7 +2498,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2512,7 +2512,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2526,7 +2526,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2540,7 +2540,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2554,7 +2554,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2568,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2582,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2610,7 +2610,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2624,7 +2624,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2638,7 +2638,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2652,7 +2652,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2666,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2694,7 +2694,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2792,7 +2792,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2803,10 +2803,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,7 +2820,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2834,7 +2834,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2848,7 +2848,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2862,7 +2862,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,7 +2876,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2890,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2904,7 +2904,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2918,7 +2918,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2932,7 +2932,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2946,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2960,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2974,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2988,7 +2988,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3002,7 +3002,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3016,7 +3016,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3030,7 +3030,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3044,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3055,10 +3055,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3086,7 +3086,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3100,7 +3100,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3114,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3128,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3142,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3156,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3170,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3198,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3212,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3240,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3254,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3268,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3282,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3296,7 +3296,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3310,7 +3310,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3324,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3352,7 +3352,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3366,7 +3366,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3380,7 +3380,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3394,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3408,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>359</v>
+        <v>325</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3422,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3436,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3450,7 +3450,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,7 +3464,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3478,7 +3478,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,7 +3492,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3506,7 +3506,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3520,7 +3520,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3534,7 +3534,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3548,7 +3548,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3562,7 +3562,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3576,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>277</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3674,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>377</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3688,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3702,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3716,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>380</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3730,7 +3730,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3741,10 +3741,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3758,7 +3758,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3772,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3786,7 +3786,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3800,7 +3800,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3814,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3828,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3842,7 +3842,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3856,7 +3856,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3870,7 +3870,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3884,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>335</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,7 +3898,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3912,7 +3912,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>346</v>
+        <v>391</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3968,7 +3968,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3979,10 +3979,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3996,7 +3996,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4010,7 +4010,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4024,7 +4024,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4038,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4052,7 +4052,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4066,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4080,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,7 +4094,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4105,10 +4105,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4122,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4136,7 +4136,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>318</v>
+        <v>405</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4150,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>406</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4164,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4178,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4192,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4206,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4220,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>378</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4234,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4248,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4259,10 +4259,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4276,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4287,10 +4287,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4304,7 +4304,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4318,7 +4318,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4332,7 +4332,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4346,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4360,7 +4360,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4374,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4388,7 +4388,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4402,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4416,7 +4416,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>312</v>
+        <v>422</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4458,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4472,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>321</v>
+        <v>426</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4486,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4500,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4511,10 +4511,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4542,7 +4542,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4553,10 +4553,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4570,7 +4570,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4581,10 +4581,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4598,7 +4598,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4612,7 +4612,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4626,7 +4626,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4640,7 +4640,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,7 +4654,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4668,7 +4668,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4682,7 +4682,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4696,7 +4696,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4710,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4724,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4738,7 +4738,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4752,7 +4752,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4766,7 +4766,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4780,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4791,10 +4791,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4808,7 +4808,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>346</v>
+        <v>450</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4822,7 +4822,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4836,7 +4836,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4850,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4864,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>451</v>
+        <v>317</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4878,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4892,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4906,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>407</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4920,7 +4920,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4931,10 +4931,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4948,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4962,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4976,7 +4976,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4987,10 +4987,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5004,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5018,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5032,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5046,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5060,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5074,7 +5074,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5088,7 +5088,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5102,7 +5102,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5116,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5130,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5158,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5172,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5186,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5200,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5214,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>471</v>
+        <v>317</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5228,7 +5228,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5242,7 +5242,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5253,10 +5253,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5270,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5284,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5312,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5326,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5340,7 +5340,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5354,7 +5354,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5368,7 +5368,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5382,7 +5382,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>483</v>
+        <v>388</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5396,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="256" spans="1:4">

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -808,667 +808,667 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9935,0.0024,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.8490,0.0001,0.0000,0.2009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0000,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9044,0.0159,0.0186,0.0068</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9221,0.0001,0.0002,0.1300</t>
+  </si>
+  <si>
+    <t>0.0065,0.0000,0.0007,0.9965</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1722,0.0051,0.7515,0.0015</t>
+  </si>
+  <si>
+    <t>0.1525,0.0010,0.8902,0.0003</t>
+  </si>
+  <si>
+    <t>0.0173,0.0001,0.9918,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.7137,0.0003,0.3327,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0111,0.9879,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7824,0.0004,0.1815,0.0030</t>
+  </si>
+  <si>
+    <t>0.7411,0.0003,0.2793,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0063,0.0030,0.9824,0.0022</t>
+  </si>
+  <si>
+    <t>0.0114,0.0002,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0927,0.0001,0.9069,0.0011</t>
+  </si>
+  <si>
+    <t>0.0049,0.0000,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0357,0.9694,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.8591,0.1420,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.9997,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0004,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.5052,0.5626,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.7714,0.0000</t>
+  </si>
+  <si>
+    <t>0.0309,0.9073,0.0185,0.0016</t>
+  </si>
+  <si>
+    <t>0.0029,0.0010,0.9883,0.0031</t>
+  </si>
+  <si>
+    <t>0.0169,0.0013,0.9658,0.0016</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.9922,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0008</t>
+  </si>
+  <si>
+    <t>0.0541,0.0430,0.0001,0.8382</t>
+  </si>
+  <si>
+    <t>0.0156,0.9253,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0065,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9961,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0003,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0026,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9920,0.0074,0.0007,0.0003</t>
+  </si>
+  <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9767,0.0050,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.0623,0.0004,0.9579,0.0005</t>
-  </si>
-  <si>
-    <t>0.4218,0.0021,0.6927,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0005,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.9298,0.0005,0.0535,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9955,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.9983,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9806,0.0007,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.9556,0.0002,0.0398,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9986,0.0006</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.0179,0.0000,0.9934,0.0000</t>
-  </si>
-  <si>
-    <t>0.0089,0.0000,0.9904,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.0000,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.2411,0.8303,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2060,0.3684,0.2232,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9994,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9921,0.0029,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9938,0.0005,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.1197,0.9040,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9917,0.2238,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.9837,0.0075,0.0008</t>
-  </si>
-  <si>
-    <t>0.0233,0.0004,0.9617,0.0019</t>
-  </si>
-  <si>
-    <t>0.0034,0.0142,0.9892,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.9944,0.0006</t>
-  </si>
-  <si>
-    <t>0.0147,0.0034,0.9878,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9849,0.0192,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9973,0.0367</t>
-  </si>
-  <si>
-    <t>0.0276,0.0612,0.0001,0.9191</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.0012,0.9973,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.0006,0.9934,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0003</t>
+    <t>0.0000,0.9935,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9989,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.9883,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9538,0.0002,0.0570,0.0001</t>
+  </si>
+  <si>
+    <t>0.1755,0.0022,0.8413,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0063,0.9980,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9939,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8159,0.9854,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.2640,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9875,0.9725,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0064,0.9985</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0009,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9930,0.7850,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9536,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9892,0.9562,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9928,0.9882,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9470,0.8480,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0065,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0028,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0007,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.9736,0.0046,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.1223,0.0000,0.9123,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9973,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1192,0.8970,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.3316,0.0018,0.6808,0.0010</t>
+  </si>
+  <si>
+    <t>0.7208,0.0001,0.3239,0.0003</t>
+  </si>
+  <si>
+    <t>0.9441,0.0042,0.0101,0.0031</t>
+  </si>
+  <si>
+    <t>0.0170,0.0035,0.9668,0.0066</t>
+  </si>
+  <si>
+    <t>0.0005,0.2650,0.0032,0.9879</t>
+  </si>
+  <si>
+    <t>0.0011,0.9960,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.9858,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6717,0.4115,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9826,0.0143,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.5896,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9234,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1932,0.0007,0.8323,0.0005</t>
+  </si>
+  <si>
+    <t>0.2476,0.0000,0.8752,0.0000</t>
+  </si>
+  <si>
+    <t>0.9664,0.0007,0.0147,0.0019</t>
+  </si>
+  <si>
+    <t>0.0146,0.0000,0.0000,0.9974</t>
+  </si>
+  <si>
+    <t>0.0000,0.9861,0.9343,0.0000</t>
+  </si>
+  <si>
+    <t>0.0170,0.9781,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.1671,0.9125,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0002,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.8810,0.0001,0.0002,0.1750</t>
+  </si>
+  <si>
+    <t>0.0015,0.0010,0.9974,0.0017</t>
+  </si>
+  <si>
+    <t>0.9927,0.0000,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.2619,0.7830,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0009,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.5746,0.2969,0.0111,0.0025</t>
+  </si>
+  <si>
+    <t>0.9724,0.0074,0.0071,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0035,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8533,0.1972,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.5683,0.5859,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1200,0.0054,0.8810,0.0012</t>
+  </si>
+  <si>
+    <t>0.9553,0.0626,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0003,0.0007</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0033,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0031,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8587,0.9889,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0081,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9691,0.0003,0.0284,0.0002</t>
-  </si>
-  <si>
-    <t>0.3990,0.0005,0.6450,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0063,0.9993,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9777,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8528,0.9638,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.2082,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9799,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0001,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0004,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0007,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9864,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.9890,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.9510,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9873,0.9191,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0039,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9825,0.0007,0.0038,0.0007</t>
-  </si>
-  <si>
-    <t>0.0588,0.0001,0.9630,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9956,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.9941,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0554,0.9463,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9832,0.0007,0.0057,0.0008</t>
-  </si>
-  <si>
-    <t>0.9278,0.0002,0.0889,0.0002</t>
-  </si>
-  <si>
-    <t>0.6434,0.0440,0.0441,0.0077</t>
-  </si>
-  <si>
-    <t>0.9595,0.0033,0.0080,0.0036</t>
-  </si>
-  <si>
-    <t>0.0053,0.3422,0.0028,0.9334</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.9614,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8437,0.1834,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9781,0.0209,0.0028,0.0004</t>
+    <t>0.9843,0.0051,0.0065,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0018,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0226,0.0004,0.9400,0.0059</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.2280,0.9850,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0129,0.0035,0.9792,0.0003</t>
+  </si>
+  <si>
+    <t>0.0645,0.0009,0.9455,0.0006</t>
+  </si>
+  <si>
+    <t>0.0427,0.0100,0.9233,0.0029</t>
+  </si>
+  <si>
+    <t>0.0404,0.0087,0.9315,0.0005</t>
+  </si>
+  <si>
+    <t>0.1168,0.0285,0.7906,0.0009</t>
+  </si>
+  <si>
+    <t>0.9756,0.0025,0.0094,0.0002</t>
+  </si>
+  <si>
+    <t>0.8599,0.0027,0.0540,0.0130</t>
+  </si>
+  <si>
+    <t>0.9212,0.0020,0.0501,0.0021</t>
+  </si>
+  <si>
+    <t>0.0072,0.9935,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9368,0.0857,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.9522,0.0757,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2930,0.7683,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9870,0.0031,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0001,0.0079,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0003,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9583,0.0027,0.0186,0.0008</t>
+  </si>
+  <si>
+    <t>0.1807,0.0032,0.8448,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0014,0.9969,0.0006</t>
+  </si>
+  <si>
+    <t>0.0110,0.0109,0.9712,0.0021</t>
+  </si>
+  <si>
+    <t>0.0106,0.0024,0.9802,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0018,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9758,0.0197,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0022,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9992,0.0007</t>
+  </si>
+  <si>
+    <t>0.0326,0.1975,0.6436,0.0012</t>
+  </si>
+  <si>
+    <t>0.8454,0.0004,0.0642,0.0087</t>
+  </si>
+  <si>
+    <t>0.0026,0.0012,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.1583,0.9659,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0005,0.9930,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0135,0.9922,0.0007</t>
+  </si>
+  <si>
+    <t>0.9812,0.0007,0.0073,0.0005</t>
+  </si>
+  <si>
+    <t>0.9253,0.0003,0.0452,0.0021</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.4877,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.3552,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0008,0.9938,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9061,0.0032,0.0427,0.0057</t>
-  </si>
-  <si>
-    <t>0.0082,0.0001,0.9944,0.0001</t>
-  </si>
-  <si>
-    <t>0.9635,0.0013,0.0113,0.0025</t>
-  </si>
-  <si>
-    <t>0.0080,0.0000,0.0000,0.9983</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9919,0.9133,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0472,0.9558,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.3207,0.8001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3088,0.0001,0.0007,0.8256</t>
-  </si>
-  <si>
-    <t>0.0009,0.0014,0.9973,0.0033</t>
-  </si>
-  <si>
-    <t>0.9761,0.0000,0.0050,0.0062</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0123,0.9866,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9923,0.0021,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.8671,0.0251,0.0284,0.0016</t>
-  </si>
-  <si>
-    <t>0.9709,0.0019,0.0175,0.0003</t>
-  </si>
-  <si>
-    <t>0.9720,0.0136,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9534,0.0311,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.8693,0.2134,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7806,0.3207,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0470,0.0005,0.9579,0.0019</t>
-  </si>
-  <si>
-    <t>0.9942,0.0061,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9831,0.0037,0.0073,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0041,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0015,0.9975,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0857,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0261,0.0016,0.9684,0.0006</t>
-  </si>
-  <si>
-    <t>0.0172,0.0019,0.9773,0.0005</t>
-  </si>
-  <si>
-    <t>0.2298,0.0017,0.7758,0.0010</t>
-  </si>
-  <si>
-    <t>0.1249,0.0151,0.7823,0.0005</t>
-  </si>
-  <si>
-    <t>0.3894,0.0238,0.5056,0.0004</t>
-  </si>
-  <si>
-    <t>0.1563,0.0010,0.9042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9637,0.0020,0.0154,0.0010</t>
-  </si>
-  <si>
-    <t>0.0798,0.0094,0.9020,0.0013</t>
-  </si>
-  <si>
-    <t>0.0024,0.9970,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9478,0.0780,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.2262,0.8578,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0236,0.9771,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5233,0.2177,0.0377,0.0008</t>
-  </si>
-  <si>
-    <t>0.8714,0.0004,0.1234,0.0010</t>
-  </si>
-  <si>
-    <t>0.9833,0.0012,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.9291,0.0097,0.0240,0.0020</t>
-  </si>
-  <si>
-    <t>0.8795,0.0005,0.1087,0.0016</t>
-  </si>
-  <si>
-    <t>0.0009,0.0007,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0261,0.0072,0.9394,0.0038</t>
-  </si>
-  <si>
-    <t>0.0048,0.0001,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0058,0.9943,0.0004</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0016,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.0311,0.5831,0.3875,0.0002</t>
-  </si>
-  <si>
-    <t>0.9815,0.0002,0.0057,0.0030</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0197,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0002,0.9935,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0036,0.9860,0.0044</t>
-  </si>
-  <si>
-    <t>0.0015,0.0034,0.9943,0.0004</t>
-  </si>
-  <si>
-    <t>0.5376,0.0065,0.2991,0.0040</t>
-  </si>
-  <si>
-    <t>0.9543,0.0008,0.0351,0.0010</t>
-  </si>
-  <si>
-    <t>0.9917,0.0001,0.0058,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0024,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0018,0.9956,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0096,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.4465,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0032,0.9922,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.0003,0.9685,0.0172</t>
-  </si>
-  <si>
-    <t>0.0044,0.0004,0.9929,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.9955,0.0077</t>
-  </si>
-  <si>
-    <t>0.9718,0.0000,0.0010,0.0201</t>
-  </si>
-  <si>
-    <t>0.0048,0.0004,0.0000,0.9986</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.9949,0.0001,0.0001,0.0015</t>
+    <t>0.9966,0.0032,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0089,0.0037,0.9752,0.0013</t>
+  </si>
+  <si>
+    <t>0.0009,0.0023,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.2078,0.9892,0.0005</t>
+  </si>
+  <si>
+    <t>0.0225,0.0036,0.9502,0.0037</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0058,0.0000,0.5269,0.1359</t>
+  </si>
+  <si>
+    <t>0.0604,0.0016,0.9166,0.0024</t>
+  </si>
+  <si>
+    <t>0.0044,0.0003,0.9921,0.0016</t>
+  </si>
+  <si>
+    <t>0.9523,0.0000,0.0024,0.0274</t>
+  </si>
+  <si>
+    <t>0.0118,0.0001,0.0000,0.9977</t>
+  </si>
+  <si>
+    <t>0.0142,0.0000,0.0000,0.9971</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1854,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1868,7 +1868,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1882,7 +1882,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1896,7 +1896,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1910,7 +1910,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1924,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1938,7 +1938,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1952,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1966,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1994,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>273</v>
@@ -2148,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2162,7 +2162,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,7 +2176,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2190,7 +2190,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2204,7 +2204,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2218,7 +2218,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2232,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2246,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,7 +2260,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,7 +2274,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2288,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2302,7 +2302,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2316,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2330,7 +2330,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2341,10 +2341,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2355,10 +2355,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2372,7 +2372,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2386,7 +2386,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2400,7 +2400,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2414,7 +2414,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2428,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2442,7 +2442,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2456,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,7 +2470,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2484,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2498,7 +2498,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2512,7 +2512,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2526,7 +2526,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2540,7 +2540,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2554,7 +2554,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2568,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2582,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2610,7 +2610,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2624,7 +2624,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2638,7 +2638,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2652,7 +2652,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2666,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2694,7 +2694,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2708,7 +2708,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2722,7 +2722,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2736,7 +2736,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2750,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2764,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2778,7 +2778,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2792,7 +2792,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2806,7 +2806,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,7 +2820,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2834,7 +2834,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2848,7 +2848,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2862,7 +2862,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,7 +2876,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2890,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2904,7 +2904,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2918,7 +2918,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2932,7 +2932,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2946,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2960,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2974,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2988,7 +2988,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3002,7 +3002,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3016,7 +3016,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3030,7 +3030,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3044,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,7 +3058,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3072,7 +3072,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3086,7 +3086,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3114,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3128,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3142,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3156,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3170,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3184,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3198,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3212,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3226,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3240,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3254,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3268,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>315</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3282,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3296,7 +3296,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3310,7 +3310,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3324,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3352,7 +3352,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>282</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3366,7 +3366,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3380,7 +3380,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3394,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3408,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3422,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3436,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3447,10 +3447,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,7 +3464,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3478,7 +3478,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3489,10 +3489,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3506,7 +3506,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3520,7 +3520,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3534,7 +3534,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3548,7 +3548,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3562,7 +3562,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3576,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,7 +3590,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3604,7 +3604,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3618,7 +3618,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3632,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>374</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3646,7 +3646,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3660,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3674,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>270</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3688,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3702,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3716,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3727,10 +3727,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3741,10 +3741,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3758,7 +3758,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3772,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3786,7 +3786,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3797,10 +3797,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3814,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3828,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3842,7 +3842,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3856,7 +3856,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3870,7 +3870,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>389</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3884,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,7 +3898,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3912,7 +3912,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>391</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3968,7 +3968,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3979,10 +3979,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3996,7 +3996,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4010,7 +4010,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4024,7 +4024,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4038,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4052,7 +4052,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4066,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4080,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,7 +4094,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4108,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4122,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4136,7 +4136,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4150,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>351</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4164,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>374</v>
+        <v>320</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4192,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>407</v>
+        <v>320</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4206,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4220,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D175" t="s">
         <v>412</v>
@@ -4553,7 +4553,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
         <v>432</v>
@@ -4581,7 +4581,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
         <v>434</v>
@@ -4637,7 +4637,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
         <v>438</v>
@@ -4721,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>444</v>
@@ -4808,7 +4808,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>450</v>
+        <v>320</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4822,7 +4822,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4836,7 +4836,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4850,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4864,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4878,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4892,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>455</v>
+        <v>416</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4906,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>271</v>
+        <v>454</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4920,7 +4920,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4931,10 +4931,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4948,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4962,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4976,7 +4976,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,7 +4990,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5004,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5018,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5032,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>464</v>
+        <v>308</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5046,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5060,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5074,7 +5074,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5088,7 +5088,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5102,7 +5102,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5116,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>271</v>
+        <v>468</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5130,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5158,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5172,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5186,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5214,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5382,7 +5382,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5396,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
